--- a/app/translations.xlsx
+++ b/app/translations.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Translations" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Translations!$A$1:$AG$394</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Translations!$A$1:$AG$396</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -15380,7 +15380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A369" authorId="0">
+    <comment ref="A371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15392,7 +15392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B369" authorId="0">
+    <comment ref="B371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15404,7 +15404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C369" authorId="0">
+    <comment ref="C371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15416,7 +15416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D369" authorId="0">
+    <comment ref="D371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15428,7 +15428,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E369" authorId="0">
+    <comment ref="E371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15440,7 +15440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F369" authorId="0">
+    <comment ref="F371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15452,7 +15452,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G369" authorId="0">
+    <comment ref="G371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15464,7 +15464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H369" authorId="0">
+    <comment ref="H371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15476,7 +15476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I369" authorId="0">
+    <comment ref="I371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15488,7 +15488,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J369" authorId="0">
+    <comment ref="J371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15500,7 +15500,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K369" authorId="0">
+    <comment ref="K371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15512,7 +15512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L369" authorId="0">
+    <comment ref="L371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15524,7 +15524,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M369" authorId="0">
+    <comment ref="M371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15536,7 +15536,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N369" authorId="0">
+    <comment ref="N371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15548,7 +15548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O369" authorId="0">
+    <comment ref="O371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15560,7 +15560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P369" authorId="0">
+    <comment ref="P371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15572,7 +15572,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q369" authorId="0">
+    <comment ref="Q371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15584,7 +15584,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R369" authorId="0">
+    <comment ref="R371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15596,7 +15596,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S369" authorId="0">
+    <comment ref="S371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15608,7 +15608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T369" authorId="0">
+    <comment ref="T371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15620,7 +15620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U369" authorId="0">
+    <comment ref="U371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15632,7 +15632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V369" authorId="0">
+    <comment ref="V371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15644,7 +15644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W369" authorId="0">
+    <comment ref="W371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15656,7 +15656,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X369" authorId="0">
+    <comment ref="X371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15668,7 +15668,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y369" authorId="0">
+    <comment ref="Y371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15680,7 +15680,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z369" authorId="0">
+    <comment ref="Z371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15692,7 +15692,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA369" authorId="0">
+    <comment ref="AA371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15704,7 +15704,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB369" authorId="0">
+    <comment ref="AB371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15716,7 +15716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC369" authorId="0">
+    <comment ref="AC371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15728,7 +15728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD369" authorId="0">
+    <comment ref="AD371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15740,7 +15740,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE369" authorId="0">
+    <comment ref="AE371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15752,7 +15752,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF369" authorId="0">
+    <comment ref="AF371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15764,7 +15764,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A370" authorId="0">
+    <comment ref="A372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15776,7 +15776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B370" authorId="0">
+    <comment ref="B372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15788,7 +15788,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C370" authorId="0">
+    <comment ref="C372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15800,7 +15800,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D370" authorId="0">
+    <comment ref="D372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15812,7 +15812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E370" authorId="0">
+    <comment ref="E372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15824,7 +15824,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F370" authorId="0">
+    <comment ref="F372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15836,7 +15836,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G370" authorId="0">
+    <comment ref="G372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15848,7 +15848,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H370" authorId="0">
+    <comment ref="H372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15860,7 +15860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I370" authorId="0">
+    <comment ref="I372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15872,7 +15872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J370" authorId="0">
+    <comment ref="J372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15884,7 +15884,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K370" authorId="0">
+    <comment ref="K372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15896,7 +15896,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L370" authorId="0">
+    <comment ref="L372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15908,7 +15908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M370" authorId="0">
+    <comment ref="M372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15920,7 +15920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N370" authorId="0">
+    <comment ref="N372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15932,7 +15932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O370" authorId="0">
+    <comment ref="O372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15944,7 +15944,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P370" authorId="0">
+    <comment ref="P372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15956,7 +15956,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q370" authorId="0">
+    <comment ref="Q372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15968,7 +15968,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R370" authorId="0">
+    <comment ref="R372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15980,7 +15980,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S370" authorId="0">
+    <comment ref="S372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15992,7 +15992,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T370" authorId="0">
+    <comment ref="T372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16004,7 +16004,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U370" authorId="0">
+    <comment ref="U372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16016,7 +16016,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V370" authorId="0">
+    <comment ref="V372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16028,7 +16028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W370" authorId="0">
+    <comment ref="W372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16040,7 +16040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X370" authorId="0">
+    <comment ref="X372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16052,7 +16052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y370" authorId="0">
+    <comment ref="Y372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16064,7 +16064,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z370" authorId="0">
+    <comment ref="Z372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16076,7 +16076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA370" authorId="0">
+    <comment ref="AA372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16088,7 +16088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB370" authorId="0">
+    <comment ref="AB372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16100,7 +16100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC370" authorId="0">
+    <comment ref="AC372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16112,7 +16112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD370" authorId="0">
+    <comment ref="AD372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16124,7 +16124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE370" authorId="0">
+    <comment ref="AE372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16136,7 +16136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF370" authorId="0">
+    <comment ref="AF372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16148,7 +16148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A373" authorId="0">
+    <comment ref="A375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16160,7 +16160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B373" authorId="0">
+    <comment ref="B375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16172,7 +16172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C373" authorId="0">
+    <comment ref="C375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16184,7 +16184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D373" authorId="0">
+    <comment ref="D375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16196,7 +16196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E373" authorId="0">
+    <comment ref="E375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16208,7 +16208,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F373" authorId="0">
+    <comment ref="F375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16220,7 +16220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G373" authorId="0">
+    <comment ref="G375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16232,7 +16232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H373" authorId="0">
+    <comment ref="H375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16244,7 +16244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I373" authorId="0">
+    <comment ref="I375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16256,7 +16256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J373" authorId="0">
+    <comment ref="J375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16268,7 +16268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K373" authorId="0">
+    <comment ref="K375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16280,7 +16280,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L373" authorId="0">
+    <comment ref="L375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16292,7 +16292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M373" authorId="0">
+    <comment ref="M375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16304,7 +16304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N373" authorId="0">
+    <comment ref="N375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16316,7 +16316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O373" authorId="0">
+    <comment ref="O375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16328,7 +16328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P373" authorId="0">
+    <comment ref="P375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16340,7 +16340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q373" authorId="0">
+    <comment ref="Q375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16352,7 +16352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R373" authorId="0">
+    <comment ref="R375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16364,7 +16364,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S373" authorId="0">
+    <comment ref="S375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16376,7 +16376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T373" authorId="0">
+    <comment ref="T375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16388,7 +16388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U373" authorId="0">
+    <comment ref="U375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16400,7 +16400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V373" authorId="0">
+    <comment ref="V375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16412,7 +16412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W373" authorId="0">
+    <comment ref="W375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16424,7 +16424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X373" authorId="0">
+    <comment ref="X375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16436,7 +16436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y373" authorId="0">
+    <comment ref="Y375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16448,7 +16448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z373" authorId="0">
+    <comment ref="Z375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16460,7 +16460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA373" authorId="0">
+    <comment ref="AA375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16472,7 +16472,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB373" authorId="0">
+    <comment ref="AB375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16484,7 +16484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC373" authorId="0">
+    <comment ref="AC375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16496,7 +16496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD373" authorId="0">
+    <comment ref="AD375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16508,7 +16508,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE373" authorId="0">
+    <comment ref="AE375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16520,7 +16520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF373" authorId="0">
+    <comment ref="AF375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16532,7 +16532,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A374" authorId="0">
+    <comment ref="A376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16544,7 +16544,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B374" authorId="0">
+    <comment ref="B376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16556,7 +16556,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C374" authorId="0">
+    <comment ref="C376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16568,7 +16568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D374" authorId="0">
+    <comment ref="D376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16580,7 +16580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E374" authorId="0">
+    <comment ref="E376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16592,7 +16592,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F374" authorId="0">
+    <comment ref="F376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16604,7 +16604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G374" authorId="0">
+    <comment ref="G376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16616,7 +16616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H374" authorId="0">
+    <comment ref="H376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16628,7 +16628,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I374" authorId="0">
+    <comment ref="I376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16640,7 +16640,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J374" authorId="0">
+    <comment ref="J376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16652,7 +16652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K374" authorId="0">
+    <comment ref="K376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16664,7 +16664,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L374" authorId="0">
+    <comment ref="L376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16676,7 +16676,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M374" authorId="0">
+    <comment ref="M376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16688,7 +16688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N374" authorId="0">
+    <comment ref="N376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16700,7 +16700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O374" authorId="0">
+    <comment ref="O376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16712,7 +16712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P374" authorId="0">
+    <comment ref="P376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16724,7 +16724,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q374" authorId="0">
+    <comment ref="Q376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16736,7 +16736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R374" authorId="0">
+    <comment ref="R376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16748,7 +16748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S374" authorId="0">
+    <comment ref="S376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16760,7 +16760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T374" authorId="0">
+    <comment ref="T376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16772,7 +16772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U374" authorId="0">
+    <comment ref="U376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16784,7 +16784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V374" authorId="0">
+    <comment ref="V376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16796,7 +16796,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W374" authorId="0">
+    <comment ref="W376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16808,7 +16808,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X374" authorId="0">
+    <comment ref="X376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16820,7 +16820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y374" authorId="0">
+    <comment ref="Y376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16832,7 +16832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z374" authorId="0">
+    <comment ref="Z376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16844,7 +16844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA374" authorId="0">
+    <comment ref="AA376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16856,7 +16856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB374" authorId="0">
+    <comment ref="AB376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16868,7 +16868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC374" authorId="0">
+    <comment ref="AC376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16880,7 +16880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD374" authorId="0">
+    <comment ref="AD376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16892,7 +16892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE374" authorId="0">
+    <comment ref="AE376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16904,7 +16904,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF374" authorId="0">
+    <comment ref="AF376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16943,7 +16943,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12608" uniqueCount="5764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12672" uniqueCount="5786">
   <si>
     <t>Key</t>
   </si>
@@ -32901,64 +32901,130 @@
     <t>預設</t>
   </si>
   <si>
-    <t>text_size</t>
-  </si>
-  <si>
-    <t>Text size</t>
-  </si>
-  <si>
-    <t>Velikost písma</t>
-  </si>
-  <si>
-    <t>Textgröße</t>
-  </si>
-  <si>
-    <t>Tamaño de texto</t>
-  </si>
-  <si>
-    <t>Taille du texte</t>
-  </si>
-  <si>
-    <t>Dimensione testo</t>
-  </si>
-  <si>
-    <t>စာလလုံးအရွယ်အစား</t>
-  </si>
-  <si>
-    <t>Skriftstørrelse</t>
-  </si>
-  <si>
-    <t>Tekstgrootte</t>
-  </si>
-  <si>
-    <t>Skriftstorleik</t>
-  </si>
-  <si>
-    <t>Rozmiar tekstu</t>
-  </si>
-  <si>
-    <t>Tamanho do texto</t>
-  </si>
-  <si>
-    <t>Mărimea textului</t>
-  </si>
-  <si>
-    <t>Размер текста</t>
-  </si>
-  <si>
-    <t>Velikost pisave</t>
-  </si>
-  <si>
-    <t>Розмір тексту</t>
-  </si>
-  <si>
-    <t>Cỡ chữ</t>
-  </si>
-  <si>
-    <t>文本大小</t>
-  </si>
-  <si>
-    <t>文字大小</t>
+    <t>text_size_note_editor</t>
+  </si>
+  <si>
+    <t>Text size (Note Editor)</t>
+  </si>
+  <si>
+    <t>Velikost písma (editor poznámek)</t>
+  </si>
+  <si>
+    <t>Textgröße (Notizeditor)</t>
+  </si>
+  <si>
+    <t>Tamaño de texto (editor de notas)</t>
+  </si>
+  <si>
+    <t>Taille du texte (éditeur de notes)</t>
+  </si>
+  <si>
+    <t>Dimensione testo (editor di note)</t>
+  </si>
+  <si>
+    <t>ဖောင့်အရွယ်အစား (မှတ်စုတည်းဖြတ်သူ)</t>
+  </si>
+  <si>
+    <t>Skriftstørrelse (notatredigering)</t>
+  </si>
+  <si>
+    <t>Tekstgrootte (notitie-editor)</t>
+  </si>
+  <si>
+    <t>Skriftstorleik (notereditor)</t>
+  </si>
+  <si>
+    <t>Rozmiar tekstu (edytor notatek)</t>
+  </si>
+  <si>
+    <t>Tamanho do texto (nota do editor)</t>
+  </si>
+  <si>
+    <t>Mărimea textului (editor de note)</t>
+  </si>
+  <si>
+    <t>Размер текста (в редакторе заметок)</t>
+  </si>
+  <si>
+    <t>Velikost pisave (urejevalnik zapiskov)</t>
+  </si>
+  <si>
+    <t>Розмір тексту (редактор нотаток)</t>
+  </si>
+  <si>
+    <t>Cỡ chữ (trình soạn thảo ghi chú)</t>
+  </si>
+  <si>
+    <t>文本大小（笔记编辑器）</t>
+  </si>
+  <si>
+    <t>字體大小（筆記編輯器）</t>
+  </si>
+  <si>
+    <t>text_size_overview</t>
+  </si>
+  <si>
+    <t>Text size (Overview)</t>
+  </si>
+  <si>
+    <t>Velikost písma (přehled)</t>
+  </si>
+  <si>
+    <t>Textgröße (Übersicht)</t>
+  </si>
+  <si>
+    <t>Tamaño de texto (descripción general)</t>
+  </si>
+  <si>
+    <t>Taille du texte (aperçu)</t>
+  </si>
+  <si>
+    <t>Dimensioni testo (panoramica)</t>
+  </si>
+  <si>
+    <t>စာသားအရွယ်အစား (ခြုံငုံသုံးသပ်ချက်)</t>
+  </si>
+  <si>
+    <t>Skriftstørrelse (oversikt)</t>
+  </si>
+  <si>
+    <t>Tekstgrootte (overzicht)</t>
+  </si>
+  <si>
+    <t>Skriftstorleik (oversikt)</t>
+  </si>
+  <si>
+    <t>Rozmiar tekstu (przegląd)</t>
+  </si>
+  <si>
+    <t>Tamanho do texto (visão geral)</t>
+  </si>
+  <si>
+    <t>Mărimea textului (prezentare generală)</t>
+  </si>
+  <si>
+    <t>Размер текста (обзор)</t>
+  </si>
+  <si>
+    <t>Velikost pisave (pregled)</t>
+  </si>
+  <si>
+    <t>Розмір тексту (огляд)</t>
+  </si>
+  <si>
+    <t>Cỡ chữ (tổng quan)</t>
+  </si>
+  <si>
+    <t>文本大小（概述）</t>
+  </si>
+  <si>
+    <t>文字大小（概述）</t>
+  </si>
+  <si>
+    <t>text_size_preview</t>
+  </si>
+  <si>
+    <t>Lorem ipsum dolor sit</t>
   </si>
   <si>
     <t>theme</t>
@@ -40192,7 +40258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF394"/>
+  <dimension ref="A1:AF396"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="50"/>
   <cols>
     <col min="1" max="1" width="40.0" customWidth="true"/>
@@ -75783,124 +75849,124 @@
       <c r="C364" t="s" s="1">
         <v>5283</v>
       </c>
-      <c r="D364" t="s" s="1">
+      <c r="D364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E364" t="s" s="1">
         <v>5284</v>
       </c>
-      <c r="E364" t="s" s="1">
+      <c r="F364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G364" t="s" s="1">
         <v>5285</v>
       </c>
-      <c r="F364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="G364" t="s" s="1">
+      <c r="H364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I364" t="s" s="1">
         <v>5286</v>
       </c>
-      <c r="H364" t="s" s="1">
+      <c r="J364" t="s" s="1">
         <v>5287</v>
       </c>
-      <c r="I364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="J364" t="s" s="1">
+      <c r="K364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M364" t="s" s="1">
         <v>5288</v>
       </c>
-      <c r="K364" t="s" s="1">
-        <v>5285</v>
-      </c>
-      <c r="L364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="M364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="N364" t="s" s="1">
+      <c r="N364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O364" t="s" s="1">
         <v>5289</v>
       </c>
-      <c r="O364" t="s" s="1">
+      <c r="P364" t="s" s="1">
         <v>5290</v>
-      </c>
-      <c r="P364" t="s" s="1">
-        <v>5284</v>
       </c>
       <c r="Q364" t="s" s="1">
         <v>5291</v>
       </c>
       <c r="R364" t="s" s="1">
-        <v>5284</v>
+        <v>5292</v>
       </c>
       <c r="S364" t="s" s="1">
-        <v>5292</v>
+        <v>5293</v>
       </c>
       <c r="T364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="U364" t="s" s="1">
-        <v>5284</v>
+        <v>5294</v>
+      </c>
+      <c r="U364" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="V364" t="s" s="1">
-        <v>5284</v>
+        <v>5295</v>
       </c>
       <c r="W364" t="s" s="1">
-        <v>5293</v>
-      </c>
-      <c r="X364" t="s" s="1">
-        <v>5285</v>
+        <v>5296</v>
+      </c>
+      <c r="X364" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="Y364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="Z364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="AA364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="AB364" t="s" s="1">
-        <v>5284</v>
+        <v>5297</v>
+      </c>
+      <c r="Z364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB364" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AC364" t="s" s="1">
-        <v>5293</v>
+        <v>5298</v>
       </c>
       <c r="AD364" t="s" s="1">
-        <v>5294</v>
+        <v>5299</v>
       </c>
       <c r="AE364" t="s" s="1">
-        <v>5295</v>
+        <v>5300</v>
       </c>
       <c r="AF364" t="s" s="1">
-        <v>5296</v>
+        <v>5301</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s" s="1">
-        <v>5297</v>
+        <v>5302</v>
       </c>
       <c r="B365" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C365" t="s" s="1">
-        <v>5298</v>
+        <v>5303</v>
       </c>
       <c r="D365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="E365" t="s" s="1">
-        <v>5299</v>
+      <c r="E365" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="F365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="G365" t="s" s="1">
-        <v>5300</v>
+      <c r="G365" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="H365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="I365" t="s" s="1">
-        <v>5301</v>
-      </c>
-      <c r="J365" t="s" s="1">
-        <v>5302</v>
+      <c r="I365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="J365" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="K365" t="s" s="2">
         <v>63</v>
@@ -75926,20 +75992,20 @@
       <c r="R365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="S365" t="s" s="1">
-        <v>5303</v>
-      </c>
-      <c r="T365" t="s" s="1">
-        <v>5304</v>
+      <c r="S365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="T365" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="U365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="V365" t="s" s="1">
-        <v>5305</v>
-      </c>
-      <c r="W365" t="s" s="1">
-        <v>5306</v>
+      <c r="V365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="W365" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="X365" t="s" s="2">
         <v>63</v>
@@ -75956,147 +76022,147 @@
       <c r="AB365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="AC365" t="s" s="1">
-        <v>5307</v>
+      <c r="AC365" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AD365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="AE365" t="s" s="1">
-        <v>5308</v>
-      </c>
-      <c r="AF365" t="s" s="1">
-        <v>5309</v>
+      <c r="AE365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AF365" t="s" s="2">
+        <v>63</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="s" s="1">
-        <v>5310</v>
+        <v>5304</v>
       </c>
       <c r="B366" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C366" t="s" s="1">
+        <v>5305</v>
+      </c>
+      <c r="D366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="E366" t="s" s="1">
+        <v>5307</v>
+      </c>
+      <c r="F366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="G366" t="s" s="1">
+        <v>5308</v>
+      </c>
+      <c r="H366" t="s" s="1">
+        <v>5309</v>
+      </c>
+      <c r="I366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="J366" t="s" s="1">
+        <v>5310</v>
+      </c>
+      <c r="K366" t="s" s="1">
+        <v>5307</v>
+      </c>
+      <c r="L366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="M366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="N366" t="s" s="1">
         <v>5311</v>
       </c>
-      <c r="D366" t="s" s="1">
+      <c r="O366" t="s" s="1">
         <v>5312</v>
       </c>
-      <c r="E366" t="s" s="1">
+      <c r="P366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="Q366" t="s" s="1">
         <v>5313</v>
       </c>
-      <c r="F366" t="s" s="1">
+      <c r="R366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="S366" t="s" s="1">
         <v>5314</v>
       </c>
-      <c r="G366" t="s" s="1">
-        <v>5314</v>
-      </c>
-      <c r="H366" t="s" s="1">
+      <c r="T366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="U366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="V366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="W366" t="s" s="1">
         <v>5315</v>
       </c>
-      <c r="I366" t="s" s="1">
+      <c r="X366" t="s" s="1">
+        <v>5307</v>
+      </c>
+      <c r="Y366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="Z366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="AA366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="AB366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="AC366" t="s" s="1">
+        <v>5315</v>
+      </c>
+      <c r="AD366" t="s" s="1">
         <v>5316</v>
       </c>
-      <c r="J366" t="s" s="1">
+      <c r="AE366" t="s" s="1">
         <v>5317</v>
       </c>
-      <c r="K366" t="s" s="1">
+      <c r="AF366" t="s" s="1">
         <v>5318</v>
-      </c>
-      <c r="L366" t="s" s="1">
-        <v>5319</v>
-      </c>
-      <c r="M366" t="s" s="1">
-        <v>5320</v>
-      </c>
-      <c r="N366" t="s" s="1">
-        <v>5321</v>
-      </c>
-      <c r="O366" t="s" s="1">
-        <v>5322</v>
-      </c>
-      <c r="P366" t="s" s="1">
-        <v>5323</v>
-      </c>
-      <c r="Q366" t="s" s="1">
-        <v>5314</v>
-      </c>
-      <c r="R366" t="s" s="1">
-        <v>5323</v>
-      </c>
-      <c r="S366" t="s" s="1">
-        <v>5324</v>
-      </c>
-      <c r="T366" t="s" s="1">
-        <v>5316</v>
-      </c>
-      <c r="U366" t="s" s="1">
-        <v>5316</v>
-      </c>
-      <c r="V366" t="s" s="1">
-        <v>5325</v>
-      </c>
-      <c r="W366" t="s" s="1">
-        <v>5326</v>
-      </c>
-      <c r="X366" t="s" s="1">
-        <v>5327</v>
-      </c>
-      <c r="Y366" t="s" s="1">
-        <v>5328</v>
-      </c>
-      <c r="Z366" t="s" s="1">
-        <v>5314</v>
-      </c>
-      <c r="AA366" t="s" s="1">
-        <v>5329</v>
-      </c>
-      <c r="AB366" t="s" s="1">
-        <v>5330</v>
-      </c>
-      <c r="AC366" t="s" s="1">
-        <v>5331</v>
-      </c>
-      <c r="AD366" t="s" s="1">
-        <v>5332</v>
-      </c>
-      <c r="AE366" t="s" s="1">
-        <v>5333</v>
-      </c>
-      <c r="AF366" t="s" s="1">
-        <v>5334</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="s" s="1">
-        <v>5335</v>
+        <v>5319</v>
       </c>
       <c r="B367" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C367" t="s" s="1">
-        <v>5336</v>
+        <v>5320</v>
       </c>
       <c r="D367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E367" t="s" s="1">
-        <v>5337</v>
+        <v>5321</v>
       </c>
       <c r="F367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G367" t="s" s="1">
-        <v>5338</v>
+        <v>5322</v>
       </c>
       <c r="H367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I367" t="s" s="1">
-        <v>5339</v>
+        <v>5323</v>
       </c>
       <c r="J367" t="s" s="1">
-        <v>5340</v>
+        <v>5324</v>
       </c>
       <c r="K367" t="s" s="2">
         <v>63</v>
@@ -76104,8 +76170,8 @@
       <c r="L367" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="M367" t="s" s="1">
-        <v>5341</v>
+      <c r="M367" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="N367" t="s" s="2">
         <v>63</v>
@@ -76116,26 +76182,26 @@
       <c r="P367" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="Q367" t="s" s="1">
-        <v>5342</v>
+      <c r="Q367" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="R367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S367" t="s" s="1">
-        <v>5343</v>
+        <v>5325</v>
       </c>
       <c r="T367" t="s" s="1">
-        <v>5344</v>
+        <v>5326</v>
       </c>
       <c r="U367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V367" t="s" s="1">
-        <v>5345</v>
+        <v>5327</v>
       </c>
       <c r="W367" t="s" s="1">
-        <v>5346</v>
+        <v>5328</v>
       </c>
       <c r="X367" t="s" s="2">
         <v>63</v>
@@ -76153,1518 +76219,1518 @@
         <v>63</v>
       </c>
       <c r="AC367" t="s" s="1">
-        <v>5347</v>
+        <v>5329</v>
       </c>
       <c r="AD367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE367" t="s" s="1">
-        <v>5348</v>
+        <v>5330</v>
       </c>
       <c r="AF367" t="s" s="1">
-        <v>5349</v>
+        <v>5331</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="s" s="1">
-        <v>5350</v>
+        <v>5332</v>
       </c>
       <c r="B368" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C368" t="s" s="1">
+        <v>5333</v>
+      </c>
+      <c r="D368" t="s" s="1">
+        <v>5334</v>
+      </c>
+      <c r="E368" t="s" s="1">
+        <v>5335</v>
+      </c>
+      <c r="F368" t="s" s="1">
+        <v>5336</v>
+      </c>
+      <c r="G368" t="s" s="1">
+        <v>5336</v>
+      </c>
+      <c r="H368" t="s" s="1">
+        <v>5337</v>
+      </c>
+      <c r="I368" t="s" s="1">
+        <v>5338</v>
+      </c>
+      <c r="J368" t="s" s="1">
+        <v>5339</v>
+      </c>
+      <c r="K368" t="s" s="1">
+        <v>5340</v>
+      </c>
+      <c r="L368" t="s" s="1">
+        <v>5341</v>
+      </c>
+      <c r="M368" t="s" s="1">
+        <v>5342</v>
+      </c>
+      <c r="N368" t="s" s="1">
+        <v>5343</v>
+      </c>
+      <c r="O368" t="s" s="1">
+        <v>5344</v>
+      </c>
+      <c r="P368" t="s" s="1">
+        <v>5345</v>
+      </c>
+      <c r="Q368" t="s" s="1">
+        <v>5336</v>
+      </c>
+      <c r="R368" t="s" s="1">
+        <v>5345</v>
+      </c>
+      <c r="S368" t="s" s="1">
+        <v>5346</v>
+      </c>
+      <c r="T368" t="s" s="1">
+        <v>5338</v>
+      </c>
+      <c r="U368" t="s" s="1">
+        <v>5338</v>
+      </c>
+      <c r="V368" t="s" s="1">
+        <v>5347</v>
+      </c>
+      <c r="W368" t="s" s="1">
+        <v>5348</v>
+      </c>
+      <c r="X368" t="s" s="1">
+        <v>5349</v>
+      </c>
+      <c r="Y368" t="s" s="1">
+        <v>5350</v>
+      </c>
+      <c r="Z368" t="s" s="1">
+        <v>5336</v>
+      </c>
+      <c r="AA368" t="s" s="1">
         <v>5351</v>
       </c>
-      <c r="D368" t="s" s="1">
+      <c r="AB368" t="s" s="1">
         <v>5352</v>
       </c>
-      <c r="E368" t="s" s="1">
+      <c r="AC368" t="s" s="1">
         <v>5353</v>
       </c>
-      <c r="F368" t="s" s="1">
+      <c r="AD368" t="s" s="1">
         <v>5354</v>
       </c>
-      <c r="G368" t="s" s="1">
+      <c r="AE368" t="s" s="1">
         <v>5355</v>
       </c>
-      <c r="H368" t="s" s="1">
+      <c r="AF368" t="s" s="1">
         <v>5356</v>
-      </c>
-      <c r="I368" t="s" s="1">
-        <v>5357</v>
-      </c>
-      <c r="J368" t="s" s="1">
-        <v>4600</v>
-      </c>
-      <c r="K368" t="s" s="1">
-        <v>5358</v>
-      </c>
-      <c r="L368" t="s" s="1">
-        <v>5359</v>
-      </c>
-      <c r="M368" t="s" s="1">
-        <v>5360</v>
-      </c>
-      <c r="N368" t="s" s="1">
-        <v>5361</v>
-      </c>
-      <c r="O368" t="s" s="1">
-        <v>5362</v>
-      </c>
-      <c r="P368" t="s" s="1">
-        <v>5363</v>
-      </c>
-      <c r="Q368" t="s" s="1">
-        <v>5364</v>
-      </c>
-      <c r="R368" t="s" s="1">
-        <v>5365</v>
-      </c>
-      <c r="S368" t="s" s="1">
-        <v>5366</v>
-      </c>
-      <c r="T368" t="s" s="1">
-        <v>5367</v>
-      </c>
-      <c r="U368" t="s" s="1">
-        <v>5367</v>
-      </c>
-      <c r="V368" t="s" s="1">
-        <v>5368</v>
-      </c>
-      <c r="W368" t="s" s="1">
-        <v>5369</v>
-      </c>
-      <c r="X368" t="s" s="1">
-        <v>5370</v>
-      </c>
-      <c r="Y368" t="s" s="1">
-        <v>5371</v>
-      </c>
-      <c r="Z368" t="s" s="1">
-        <v>5372</v>
-      </c>
-      <c r="AA368" t="s" s="1">
-        <v>5373</v>
-      </c>
-      <c r="AB368" t="s" s="1">
-        <v>5374</v>
-      </c>
-      <c r="AC368" t="s" s="1">
-        <v>5375</v>
-      </c>
-      <c r="AD368" t="s" s="1">
-        <v>5376</v>
-      </c>
-      <c r="AE368" t="s" s="1">
-        <v>5377</v>
-      </c>
-      <c r="AF368" t="s" s="1">
-        <v>5378</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s" s="1">
-        <v>5379</v>
+        <v>5357</v>
       </c>
       <c r="B369" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="D369" t="s" s="3">
+      <c r="C369" t="s" s="1">
+        <v>5358</v>
+      </c>
+      <c r="D369" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E369" t="s" s="1">
-        <v>4621</v>
-      </c>
-      <c r="F369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="G369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="H369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="I369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="J369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="K369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="L369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="M369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="N369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="O369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="P369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Q369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="R369" t="s" s="3">
+        <v>5359</v>
+      </c>
+      <c r="F369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G369" t="s" s="1">
+        <v>5360</v>
+      </c>
+      <c r="H369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I369" t="s" s="1">
+        <v>5361</v>
+      </c>
+      <c r="J369" t="s" s="1">
+        <v>5362</v>
+      </c>
+      <c r="K369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M369" t="s" s="1">
+        <v>5363</v>
+      </c>
+      <c r="N369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q369" t="s" s="1">
+        <v>5364</v>
+      </c>
+      <c r="R369" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S369" t="s" s="1">
-        <v>5380</v>
-      </c>
-      <c r="T369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="U369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="V369" t="s" s="3">
-        <v>63</v>
+        <v>5365</v>
+      </c>
+      <c r="T369" t="s" s="1">
+        <v>5366</v>
+      </c>
+      <c r="U369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V369" t="s" s="1">
+        <v>5367</v>
       </c>
       <c r="W369" t="s" s="1">
-        <v>5381</v>
-      </c>
-      <c r="X369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Y369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Z369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AA369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AB369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AC369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AD369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AE369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AF369" t="s" s="3">
-        <v>63</v>
+        <v>5368</v>
+      </c>
+      <c r="X369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC369" t="s" s="1">
+        <v>5369</v>
+      </c>
+      <c r="AD369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE369" t="s" s="1">
+        <v>5370</v>
+      </c>
+      <c r="AF369" t="s" s="1">
+        <v>5371</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="s" s="1">
-        <v>5382</v>
+        <v>5372</v>
       </c>
       <c r="B370" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="D370" t="s" s="3">
-        <v>63</v>
+      <c r="C370" t="s" s="1">
+        <v>5373</v>
+      </c>
+      <c r="D370" t="s" s="1">
+        <v>5374</v>
       </c>
       <c r="E370" t="s" s="1">
-        <v>4625</v>
-      </c>
-      <c r="F370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="G370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="H370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="I370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="J370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="K370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="L370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="M370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="N370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="O370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="P370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Q370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="R370" t="s" s="3">
-        <v>63</v>
+        <v>5375</v>
+      </c>
+      <c r="F370" t="s" s="1">
+        <v>5376</v>
+      </c>
+      <c r="G370" t="s" s="1">
+        <v>5377</v>
+      </c>
+      <c r="H370" t="s" s="1">
+        <v>5378</v>
+      </c>
+      <c r="I370" t="s" s="1">
+        <v>5379</v>
+      </c>
+      <c r="J370" t="s" s="1">
+        <v>4600</v>
+      </c>
+      <c r="K370" t="s" s="1">
+        <v>5380</v>
+      </c>
+      <c r="L370" t="s" s="1">
+        <v>5381</v>
+      </c>
+      <c r="M370" t="s" s="1">
+        <v>5382</v>
+      </c>
+      <c r="N370" t="s" s="1">
+        <v>5383</v>
+      </c>
+      <c r="O370" t="s" s="1">
+        <v>5384</v>
+      </c>
+      <c r="P370" t="s" s="1">
+        <v>5385</v>
+      </c>
+      <c r="Q370" t="s" s="1">
+        <v>5386</v>
+      </c>
+      <c r="R370" t="s" s="1">
+        <v>5387</v>
       </c>
       <c r="S370" t="s" s="1">
-        <v>5383</v>
-      </c>
-      <c r="T370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="U370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="V370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="W370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="X370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Y370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Z370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AA370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AB370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AC370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AD370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AE370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AF370" t="s" s="3">
-        <v>63</v>
+        <v>5388</v>
+      </c>
+      <c r="T370" t="s" s="1">
+        <v>5389</v>
+      </c>
+      <c r="U370" t="s" s="1">
+        <v>5389</v>
+      </c>
+      <c r="V370" t="s" s="1">
+        <v>5390</v>
+      </c>
+      <c r="W370" t="s" s="1">
+        <v>5391</v>
+      </c>
+      <c r="X370" t="s" s="1">
+        <v>5392</v>
+      </c>
+      <c r="Y370" t="s" s="1">
+        <v>5393</v>
+      </c>
+      <c r="Z370" t="s" s="1">
+        <v>5394</v>
+      </c>
+      <c r="AA370" t="s" s="1">
+        <v>5395</v>
+      </c>
+      <c r="AB370" t="s" s="1">
+        <v>5396</v>
+      </c>
+      <c r="AC370" t="s" s="1">
+        <v>5397</v>
+      </c>
+      <c r="AD370" t="s" s="1">
+        <v>5398</v>
+      </c>
+      <c r="AE370" t="s" s="1">
+        <v>5399</v>
+      </c>
+      <c r="AF370" t="s" s="1">
+        <v>5400</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="s" s="1">
-        <v>5384</v>
+        <v>5401</v>
       </c>
       <c r="B371" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C371" t="s" s="1">
-        <v>5385</v>
-      </c>
-      <c r="D371" t="s" s="2">
+      <c r="C371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="D371" t="s" s="3">
         <v>63</v>
       </c>
       <c r="E371" t="s" s="1">
         <v>4621</v>
       </c>
-      <c r="F371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G371" t="s" s="1">
-        <v>5386</v>
-      </c>
-      <c r="H371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I371" t="s" s="1">
-        <v>5387</v>
-      </c>
-      <c r="J371" t="s" s="1">
-        <v>5388</v>
-      </c>
-      <c r="K371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M371" t="s" s="1">
-        <v>5389</v>
-      </c>
-      <c r="N371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q371" t="s" s="1">
-        <v>5390</v>
-      </c>
-      <c r="R371" t="s" s="2">
+      <c r="F371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="G371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="H371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="I371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="J371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="K371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="L371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="M371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="N371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="O371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="P371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Q371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="R371" t="s" s="3">
         <v>63</v>
       </c>
       <c r="S371" t="s" s="1">
-        <v>5391</v>
-      </c>
-      <c r="T371" t="s" s="1">
-        <v>5392</v>
-      </c>
-      <c r="U371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V371" t="s" s="1">
-        <v>5393</v>
+        <v>5402</v>
+      </c>
+      <c r="T371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="U371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="V371" t="s" s="3">
+        <v>63</v>
       </c>
       <c r="W371" t="s" s="1">
-        <v>5394</v>
-      </c>
-      <c r="X371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC371" t="s" s="1">
-        <v>5395</v>
-      </c>
-      <c r="AD371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE371" t="s" s="1">
-        <v>5396</v>
-      </c>
-      <c r="AF371" t="s" s="1">
-        <v>5397</v>
+        <v>5403</v>
+      </c>
+      <c r="X371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Y371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Z371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AA371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AB371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AC371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AD371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AE371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AF371" t="s" s="3">
+        <v>63</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="s" s="1">
-        <v>5398</v>
+        <v>5404</v>
       </c>
       <c r="B372" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C372" t="s" s="1">
-        <v>5399</v>
-      </c>
-      <c r="D372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="F372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G372" t="s" s="1">
-        <v>5400</v>
-      </c>
-      <c r="H372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I372" t="s" s="1">
-        <v>5401</v>
-      </c>
-      <c r="J372" t="s" s="1">
-        <v>5402</v>
-      </c>
-      <c r="K372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M372" t="s" s="1">
-        <v>5403</v>
-      </c>
-      <c r="N372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q372" t="s" s="1">
-        <v>5404</v>
-      </c>
-      <c r="R372" t="s" s="2">
+      <c r="C372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="D372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="E372" t="s" s="1">
+        <v>4625</v>
+      </c>
+      <c r="F372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="G372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="H372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="I372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="J372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="K372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="L372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="M372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="N372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="O372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="P372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Q372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="R372" t="s" s="3">
         <v>63</v>
       </c>
       <c r="S372" t="s" s="1">
-        <v>5383</v>
-      </c>
-      <c r="T372" t="s" s="1">
         <v>5405</v>
       </c>
-      <c r="U372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V372" t="s" s="1">
-        <v>5406</v>
-      </c>
-      <c r="W372" t="s" s="1">
-        <v>5407</v>
-      </c>
-      <c r="X372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC372" t="s" s="1">
-        <v>5395</v>
-      </c>
-      <c r="AD372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE372" t="s" s="1">
-        <v>5396</v>
-      </c>
-      <c r="AF372" t="s" s="1">
-        <v>5397</v>
+      <c r="T372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="U372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="V372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="W372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="X372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Y372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Z372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AA372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AB372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AC372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AD372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AE372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AF372" t="s" s="3">
+        <v>63</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="s" s="1">
-        <v>5408</v>
+        <v>5406</v>
       </c>
       <c r="B373" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="D373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="E373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="F373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="G373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="H373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="I373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="J373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="K373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="L373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="M373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="N373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="O373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="P373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Q373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="R373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="S373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="T373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="U373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="V373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="W373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="X373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Y373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Z373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AA373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AB373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AC373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AD373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AE373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AF373" t="s" s="3">
-        <v>63</v>
+      <c r="C373" t="s" s="1">
+        <v>5407</v>
+      </c>
+      <c r="D373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E373" t="s" s="1">
+        <v>4621</v>
+      </c>
+      <c r="F373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G373" t="s" s="1">
+        <v>5408</v>
+      </c>
+      <c r="H373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I373" t="s" s="1">
+        <v>5409</v>
+      </c>
+      <c r="J373" t="s" s="1">
+        <v>5410</v>
+      </c>
+      <c r="K373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M373" t="s" s="1">
+        <v>5411</v>
+      </c>
+      <c r="N373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q373" t="s" s="1">
+        <v>5412</v>
+      </c>
+      <c r="R373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S373" t="s" s="1">
+        <v>5413</v>
+      </c>
+      <c r="T373" t="s" s="1">
+        <v>5414</v>
+      </c>
+      <c r="U373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V373" t="s" s="1">
+        <v>5415</v>
+      </c>
+      <c r="W373" t="s" s="1">
+        <v>5416</v>
+      </c>
+      <c r="X373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC373" t="s" s="1">
+        <v>5417</v>
+      </c>
+      <c r="AD373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE373" t="s" s="1">
+        <v>5418</v>
+      </c>
+      <c r="AF373" t="s" s="1">
+        <v>5419</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="s" s="1">
-        <v>5409</v>
+        <v>5420</v>
       </c>
       <c r="B374" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="D374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="E374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="F374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="G374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="H374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="I374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="J374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="K374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="L374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="M374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="N374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="O374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="P374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Q374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="R374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="S374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="T374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="U374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="V374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="W374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="X374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Y374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Z374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AA374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AB374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AC374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AD374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AE374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AF374" t="s" s="3">
-        <v>63</v>
+      <c r="C374" t="s" s="1">
+        <v>5421</v>
+      </c>
+      <c r="D374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G374" t="s" s="1">
+        <v>5422</v>
+      </c>
+      <c r="H374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I374" t="s" s="1">
+        <v>5423</v>
+      </c>
+      <c r="J374" t="s" s="1">
+        <v>5424</v>
+      </c>
+      <c r="K374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M374" t="s" s="1">
+        <v>5425</v>
+      </c>
+      <c r="N374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q374" t="s" s="1">
+        <v>5426</v>
+      </c>
+      <c r="R374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S374" t="s" s="1">
+        <v>5405</v>
+      </c>
+      <c r="T374" t="s" s="1">
+        <v>5427</v>
+      </c>
+      <c r="U374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V374" t="s" s="1">
+        <v>5428</v>
+      </c>
+      <c r="W374" t="s" s="1">
+        <v>5429</v>
+      </c>
+      <c r="X374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC374" t="s" s="1">
+        <v>5417</v>
+      </c>
+      <c r="AD374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE374" t="s" s="1">
+        <v>5418</v>
+      </c>
+      <c r="AF374" t="s" s="1">
+        <v>5419</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s" s="1">
-        <v>5410</v>
+        <v>5430</v>
       </c>
       <c r="B375" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C375" t="s" s="1">
-        <v>5411</v>
-      </c>
-      <c r="D375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E375" t="s" s="1">
-        <v>5412</v>
-      </c>
-      <c r="F375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G375" t="s" s="1">
-        <v>5413</v>
-      </c>
-      <c r="H375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I375" t="s" s="1">
-        <v>5414</v>
-      </c>
-      <c r="J375" t="s" s="1">
-        <v>5415</v>
-      </c>
-      <c r="K375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M375" t="s" s="1">
-        <v>5416</v>
-      </c>
-      <c r="N375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q375" t="s" s="1">
-        <v>5417</v>
-      </c>
-      <c r="R375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S375" t="s" s="1">
-        <v>5418</v>
-      </c>
-      <c r="T375" t="s" s="1">
-        <v>5419</v>
-      </c>
-      <c r="U375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V375" t="s" s="1">
-        <v>5420</v>
-      </c>
-      <c r="W375" t="s" s="1">
-        <v>5421</v>
-      </c>
-      <c r="X375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC375" t="s" s="1">
-        <v>5422</v>
-      </c>
-      <c r="AD375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE375" t="s" s="1">
-        <v>5423</v>
-      </c>
-      <c r="AF375" t="s" s="1">
-        <v>5424</v>
+      <c r="C375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="D375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="E375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="F375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="G375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="H375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="I375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="J375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="K375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="L375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="M375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="N375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="O375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="P375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Q375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="R375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="S375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="T375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="U375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="V375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="W375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="X375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Y375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Z375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AA375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AB375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AC375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AD375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AE375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AF375" t="s" s="3">
+        <v>63</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="s" s="1">
-        <v>5425</v>
+        <v>5431</v>
       </c>
       <c r="B376" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C376" t="s" s="1">
-        <v>5426</v>
-      </c>
-      <c r="D376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E376" t="s" s="1">
-        <v>572</v>
-      </c>
-      <c r="F376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G376" t="s" s="1">
-        <v>5427</v>
-      </c>
-      <c r="H376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I376" t="s" s="1">
-        <v>5428</v>
-      </c>
-      <c r="J376" t="s" s="1">
-        <v>871</v>
-      </c>
-      <c r="K376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M376" t="s" s="1">
-        <v>874</v>
-      </c>
-      <c r="N376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q376" t="s" s="1">
-        <v>5429</v>
-      </c>
-      <c r="R376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S376" t="s" s="1">
-        <v>577</v>
-      </c>
-      <c r="T376" t="s" s="1">
-        <v>5430</v>
-      </c>
-      <c r="U376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V376" t="s" s="1">
-        <v>5431</v>
-      </c>
-      <c r="W376" t="s" s="1">
-        <v>4417</v>
-      </c>
-      <c r="X376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC376" t="s" s="1">
-        <v>5432</v>
-      </c>
-      <c r="AD376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE376" t="s" s="1">
-        <v>5433</v>
-      </c>
-      <c r="AF376" t="s" s="1">
-        <v>5434</v>
+      <c r="C376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="D376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="E376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="F376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="G376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="H376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="I376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="J376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="K376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="L376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="M376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="N376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="O376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="P376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Q376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="R376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="S376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="T376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="U376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="V376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="W376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="X376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Y376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Z376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AA376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AB376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AC376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AD376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AE376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AF376" t="s" s="3">
+        <v>63</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="s" s="1">
-        <v>5435</v>
+        <v>5432</v>
       </c>
       <c r="B377" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C377" t="s" s="1">
+        <v>5433</v>
+      </c>
+      <c r="D377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E377" t="s" s="1">
+        <v>5434</v>
+      </c>
+      <c r="F377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G377" t="s" s="1">
+        <v>5435</v>
+      </c>
+      <c r="H377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I377" t="s" s="1">
         <v>5436</v>
       </c>
-      <c r="D377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E377" t="s" s="1">
+      <c r="J377" t="s" s="1">
         <v>5437</v>
       </c>
-      <c r="F377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G377" t="s" s="1">
+      <c r="K377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M377" t="s" s="1">
         <v>5438</v>
       </c>
-      <c r="H377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I377" t="s" s="1">
+      <c r="N377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q377" t="s" s="1">
         <v>5439</v>
       </c>
-      <c r="J377" t="s" s="1">
+      <c r="R377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S377" t="s" s="1">
         <v>5440</v>
       </c>
-      <c r="K377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M377" t="s" s="1">
+      <c r="T377" t="s" s="1">
         <v>5441</v>
       </c>
-      <c r="N377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P377" t="s" s="1">
+      <c r="U377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V377" t="s" s="1">
         <v>5442</v>
       </c>
-      <c r="Q377" t="s" s="1">
+      <c r="W377" t="s" s="1">
         <v>5443</v>
       </c>
-      <c r="R377" t="s" s="1">
+      <c r="X377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC377" t="s" s="1">
         <v>5444</v>
       </c>
-      <c r="S377" t="s" s="1">
+      <c r="AD377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE377" t="s" s="1">
         <v>5445</v>
       </c>
-      <c r="T377" t="s" s="1">
+      <c r="AF377" t="s" s="1">
         <v>5446</v>
-      </c>
-      <c r="U377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V377" t="s" s="1">
-        <v>5447</v>
-      </c>
-      <c r="W377" t="s" s="1">
-        <v>5448</v>
-      </c>
-      <c r="X377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y377" t="s" s="1">
-        <v>5449</v>
-      </c>
-      <c r="Z377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC377" t="s" s="1">
-        <v>5450</v>
-      </c>
-      <c r="AD377" t="s" s="1">
-        <v>5451</v>
-      </c>
-      <c r="AE377" t="s" s="1">
-        <v>5452</v>
-      </c>
-      <c r="AF377" t="s" s="1">
-        <v>5453</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="s" s="1">
-        <v>5454</v>
+        <v>5447</v>
       </c>
       <c r="B378" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C378" t="s" s="1">
+        <v>5448</v>
+      </c>
+      <c r="D378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E378" t="s" s="1">
+        <v>572</v>
+      </c>
+      <c r="F378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G378" t="s" s="1">
+        <v>5449</v>
+      </c>
+      <c r="H378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I378" t="s" s="1">
+        <v>5450</v>
+      </c>
+      <c r="J378" t="s" s="1">
+        <v>871</v>
+      </c>
+      <c r="K378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M378" t="s" s="1">
+        <v>874</v>
+      </c>
+      <c r="N378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q378" t="s" s="1">
+        <v>5451</v>
+      </c>
+      <c r="R378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S378" t="s" s="1">
+        <v>577</v>
+      </c>
+      <c r="T378" t="s" s="1">
+        <v>5452</v>
+      </c>
+      <c r="U378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V378" t="s" s="1">
+        <v>5453</v>
+      </c>
+      <c r="W378" t="s" s="1">
+        <v>4417</v>
+      </c>
+      <c r="X378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC378" t="s" s="1">
+        <v>5454</v>
+      </c>
+      <c r="AD378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE378" t="s" s="1">
         <v>5455</v>
       </c>
-      <c r="D378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E378" t="s" s="1">
+      <c r="AF378" t="s" s="1">
         <v>5456</v>
-      </c>
-      <c r="F378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G378" t="s" s="1">
-        <v>5457</v>
-      </c>
-      <c r="H378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I378" t="s" s="1">
-        <v>5458</v>
-      </c>
-      <c r="J378" t="s" s="1">
-        <v>5459</v>
-      </c>
-      <c r="K378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M378" t="s" s="1">
-        <v>5460</v>
-      </c>
-      <c r="N378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P378" t="s" s="1">
-        <v>5461</v>
-      </c>
-      <c r="Q378" t="s" s="1">
-        <v>5462</v>
-      </c>
-      <c r="R378" t="s" s="1">
-        <v>5463</v>
-      </c>
-      <c r="S378" t="s" s="1">
-        <v>5464</v>
-      </c>
-      <c r="T378" t="s" s="1">
-        <v>5465</v>
-      </c>
-      <c r="U378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V378" t="s" s="1">
-        <v>5466</v>
-      </c>
-      <c r="W378" t="s" s="1">
-        <v>5467</v>
-      </c>
-      <c r="X378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y378" t="s" s="1">
-        <v>5468</v>
-      </c>
-      <c r="Z378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC378" t="s" s="1">
-        <v>5469</v>
-      </c>
-      <c r="AD378" t="s" s="1">
-        <v>5470</v>
-      </c>
-      <c r="AE378" t="s" s="1">
-        <v>5471</v>
-      </c>
-      <c r="AF378" t="s" s="1">
-        <v>5472</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="s" s="1">
-        <v>5473</v>
+        <v>5457</v>
       </c>
       <c r="B379" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C379" t="s" s="1">
+        <v>5458</v>
+      </c>
+      <c r="D379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E379" t="s" s="1">
+        <v>5459</v>
+      </c>
+      <c r="F379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G379" t="s" s="1">
+        <v>5460</v>
+      </c>
+      <c r="H379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I379" t="s" s="1">
+        <v>5461</v>
+      </c>
+      <c r="J379" t="s" s="1">
+        <v>5462</v>
+      </c>
+      <c r="K379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M379" t="s" s="1">
+        <v>5463</v>
+      </c>
+      <c r="N379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P379" t="s" s="1">
+        <v>5464</v>
+      </c>
+      <c r="Q379" t="s" s="1">
+        <v>5465</v>
+      </c>
+      <c r="R379" t="s" s="1">
+        <v>5466</v>
+      </c>
+      <c r="S379" t="s" s="1">
+        <v>5467</v>
+      </c>
+      <c r="T379" t="s" s="1">
+        <v>5468</v>
+      </c>
+      <c r="U379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V379" t="s" s="1">
+        <v>5469</v>
+      </c>
+      <c r="W379" t="s" s="1">
+        <v>5470</v>
+      </c>
+      <c r="X379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y379" t="s" s="1">
+        <v>5471</v>
+      </c>
+      <c r="Z379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC379" t="s" s="1">
+        <v>5472</v>
+      </c>
+      <c r="AD379" t="s" s="1">
+        <v>5473</v>
+      </c>
+      <c r="AE379" t="s" s="1">
         <v>5474</v>
       </c>
-      <c r="D379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E379" t="s" s="1">
+      <c r="AF379" t="s" s="1">
         <v>5475</v>
-      </c>
-      <c r="F379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G379" t="s" s="1">
-        <v>5476</v>
-      </c>
-      <c r="H379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I379" t="s" s="1">
-        <v>5477</v>
-      </c>
-      <c r="J379" t="s" s="1">
-        <v>5478</v>
-      </c>
-      <c r="K379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M379" t="s" s="1">
-        <v>5479</v>
-      </c>
-      <c r="N379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S379" t="s" s="1">
-        <v>5480</v>
-      </c>
-      <c r="T379" t="s" s="1">
-        <v>5481</v>
-      </c>
-      <c r="U379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V379" t="s" s="1">
-        <v>5482</v>
-      </c>
-      <c r="W379" t="s" s="1">
-        <v>5483</v>
-      </c>
-      <c r="X379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC379" t="s" s="1">
-        <v>5484</v>
-      </c>
-      <c r="AD379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE379" t="s" s="1">
-        <v>5485</v>
-      </c>
-      <c r="AF379" t="s" s="1">
-        <v>5486</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s" s="1">
-        <v>5487</v>
+        <v>5476</v>
       </c>
       <c r="B380" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C380" t="s" s="1">
+        <v>5477</v>
+      </c>
+      <c r="D380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E380" t="s" s="1">
+        <v>5478</v>
+      </c>
+      <c r="F380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G380" t="s" s="1">
+        <v>5479</v>
+      </c>
+      <c r="H380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I380" t="s" s="1">
+        <v>5480</v>
+      </c>
+      <c r="J380" t="s" s="1">
+        <v>5481</v>
+      </c>
+      <c r="K380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M380" t="s" s="1">
+        <v>5482</v>
+      </c>
+      <c r="N380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P380" t="s" s="1">
+        <v>5483</v>
+      </c>
+      <c r="Q380" t="s" s="1">
+        <v>5484</v>
+      </c>
+      <c r="R380" t="s" s="1">
+        <v>5485</v>
+      </c>
+      <c r="S380" t="s" s="1">
+        <v>5486</v>
+      </c>
+      <c r="T380" t="s" s="1">
+        <v>5487</v>
+      </c>
+      <c r="U380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V380" t="s" s="1">
         <v>5488</v>
       </c>
-      <c r="D380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E380" t="s" s="1">
+      <c r="W380" t="s" s="1">
         <v>5489</v>
       </c>
-      <c r="F380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G380" t="s" s="1">
+      <c r="X380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y380" t="s" s="1">
         <v>5490</v>
       </c>
-      <c r="H380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I380" t="s" s="1">
+      <c r="Z380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC380" t="s" s="1">
         <v>5491</v>
       </c>
-      <c r="J380" t="s" s="1">
+      <c r="AD380" t="s" s="1">
         <v>5492</v>
       </c>
-      <c r="K380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M380" t="s" s="1">
+      <c r="AE380" t="s" s="1">
         <v>5493</v>
       </c>
-      <c r="N380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q380" t="s" s="1">
+      <c r="AF380" t="s" s="1">
         <v>5494</v>
-      </c>
-      <c r="R380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S380" t="s" s="1">
-        <v>5495</v>
-      </c>
-      <c r="T380" t="s" s="1">
-        <v>5496</v>
-      </c>
-      <c r="U380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V380" t="s" s="1">
-        <v>5497</v>
-      </c>
-      <c r="W380" t="s" s="1">
-        <v>5498</v>
-      </c>
-      <c r="X380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC380" t="s" s="1">
-        <v>5499</v>
-      </c>
-      <c r="AD380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE380" t="s" s="1">
-        <v>5500</v>
-      </c>
-      <c r="AF380" t="s" s="1">
-        <v>5501</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="s" s="1">
-        <v>5502</v>
+        <v>5495</v>
       </c>
       <c r="B381" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C381" t="s" s="1">
+        <v>5496</v>
+      </c>
+      <c r="D381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E381" t="s" s="1">
+        <v>5497</v>
+      </c>
+      <c r="F381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G381" t="s" s="1">
+        <v>5498</v>
+      </c>
+      <c r="H381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I381" t="s" s="1">
+        <v>5499</v>
+      </c>
+      <c r="J381" t="s" s="1">
+        <v>5500</v>
+      </c>
+      <c r="K381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M381" t="s" s="1">
+        <v>5501</v>
+      </c>
+      <c r="N381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S381" t="s" s="1">
+        <v>5502</v>
+      </c>
+      <c r="T381" t="s" s="1">
         <v>5503</v>
       </c>
-      <c r="D381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E381" t="s" s="1">
+      <c r="U381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V381" t="s" s="1">
         <v>5504</v>
       </c>
-      <c r="F381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G381" t="s" s="1">
+      <c r="W381" t="s" s="1">
         <v>5505</v>
       </c>
-      <c r="H381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I381" t="s" s="1">
+      <c r="X381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC381" t="s" s="1">
         <v>5506</v>
       </c>
-      <c r="J381" t="s" s="1">
+      <c r="AD381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE381" t="s" s="1">
         <v>5507</v>
       </c>
-      <c r="K381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M381" t="s" s="1">
+      <c r="AF381" t="s" s="1">
         <v>5508</v>
-      </c>
-      <c r="N381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S381" t="s" s="1">
-        <v>5509</v>
-      </c>
-      <c r="T381" t="s" s="1">
-        <v>5510</v>
-      </c>
-      <c r="U381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V381" t="s" s="1">
-        <v>5511</v>
-      </c>
-      <c r="W381" t="s" s="1">
-        <v>5512</v>
-      </c>
-      <c r="X381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC381" t="s" s="1">
-        <v>5513</v>
-      </c>
-      <c r="AD381" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE381" t="s" s="1">
-        <v>5514</v>
-      </c>
-      <c r="AF381" t="s" s="1">
-        <v>5515</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="s" s="1">
-        <v>5516</v>
+        <v>5509</v>
       </c>
       <c r="B382" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C382" t="s" s="1">
+        <v>5510</v>
+      </c>
+      <c r="D382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E382" t="s" s="1">
+        <v>5511</v>
+      </c>
+      <c r="F382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G382" t="s" s="1">
+        <v>5512</v>
+      </c>
+      <c r="H382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I382" t="s" s="1">
+        <v>5513</v>
+      </c>
+      <c r="J382" t="s" s="1">
+        <v>5514</v>
+      </c>
+      <c r="K382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M382" t="s" s="1">
+        <v>5515</v>
+      </c>
+      <c r="N382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q382" t="s" s="1">
+        <v>5516</v>
+      </c>
+      <c r="R382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S382" t="s" s="1">
         <v>5517</v>
       </c>
-      <c r="D382" t="s" s="1">
+      <c r="T382" t="s" s="1">
         <v>5518</v>
       </c>
-      <c r="E382" t="s" s="1">
+      <c r="U382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V382" t="s" s="1">
         <v>5519</v>
       </c>
-      <c r="F382" t="s" s="1">
+      <c r="W382" t="s" s="1">
         <v>5520</v>
       </c>
-      <c r="G382" t="s" s="1">
+      <c r="X382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC382" t="s" s="1">
         <v>5521</v>
       </c>
-      <c r="H382" t="s" s="1">
+      <c r="AD382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE382" t="s" s="1">
         <v>5522</v>
       </c>
-      <c r="I382" t="s" s="1">
+      <c r="AF382" t="s" s="1">
         <v>5523</v>
-      </c>
-      <c r="J382" t="s" s="1">
-        <v>5524</v>
-      </c>
-      <c r="K382" t="s" s="1">
-        <v>5525</v>
-      </c>
-      <c r="L382" t="s" s="1">
-        <v>5526</v>
-      </c>
-      <c r="M382" t="s" s="1">
-        <v>5527</v>
-      </c>
-      <c r="N382" t="s" s="1">
-        <v>5528</v>
-      </c>
-      <c r="O382" t="s" s="1">
-        <v>5529</v>
-      </c>
-      <c r="P382" t="s" s="1">
-        <v>5530</v>
-      </c>
-      <c r="Q382" t="s" s="1">
-        <v>5531</v>
-      </c>
-      <c r="R382" t="s" s="1">
-        <v>5532</v>
-      </c>
-      <c r="S382" t="s" s="1">
-        <v>5533</v>
-      </c>
-      <c r="T382" t="s" s="1">
-        <v>5534</v>
-      </c>
-      <c r="U382" t="s" s="1">
-        <v>5534</v>
-      </c>
-      <c r="V382" t="s" s="1">
-        <v>5535</v>
-      </c>
-      <c r="W382" t="s" s="1">
-        <v>5536</v>
-      </c>
-      <c r="X382" t="s" s="1">
-        <v>5537</v>
-      </c>
-      <c r="Y382" t="s" s="1">
-        <v>5538</v>
-      </c>
-      <c r="Z382" t="s" s="1">
-        <v>5539</v>
-      </c>
-      <c r="AA382" t="s" s="1">
-        <v>5540</v>
-      </c>
-      <c r="AB382" t="s" s="1">
-        <v>5541</v>
-      </c>
-      <c r="AC382" t="s" s="1">
-        <v>5542</v>
-      </c>
-      <c r="AD382" t="s" s="1">
-        <v>5543</v>
-      </c>
-      <c r="AE382" t="s" s="1">
-        <v>5544</v>
-      </c>
-      <c r="AF382" t="s" s="1">
-        <v>5545</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s" s="1">
-        <v>5546</v>
+        <v>5524</v>
       </c>
       <c r="B383" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C383" t="s" s="1">
-        <v>5547</v>
+        <v>5525</v>
       </c>
       <c r="D383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E383" t="s" s="1">
-        <v>5548</v>
+        <v>5526</v>
       </c>
       <c r="F383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G383" t="s" s="1">
-        <v>5549</v>
+        <v>5527</v>
       </c>
       <c r="H383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I383" t="s" s="1">
-        <v>3923</v>
+        <v>5528</v>
       </c>
       <c r="J383" t="s" s="1">
-        <v>5550</v>
+        <v>5529</v>
       </c>
       <c r="K383" t="s" s="2">
         <v>63</v>
@@ -77673,7 +77739,7 @@
         <v>63</v>
       </c>
       <c r="M383" t="s" s="1">
-        <v>3921</v>
+        <v>5530</v>
       </c>
       <c r="N383" t="s" s="2">
         <v>63</v>
@@ -77691,19 +77757,19 @@
         <v>63</v>
       </c>
       <c r="S383" t="s" s="1">
-        <v>5551</v>
+        <v>5531</v>
       </c>
       <c r="T383" t="s" s="1">
-        <v>5552</v>
+        <v>5532</v>
       </c>
       <c r="U383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V383" t="s" s="1">
-        <v>5553</v>
+        <v>5533</v>
       </c>
       <c r="W383" t="s" s="1">
-        <v>5554</v>
+        <v>5534</v>
       </c>
       <c r="X383" t="s" s="2">
         <v>63</v>
@@ -77721,289 +77787,289 @@
         <v>63</v>
       </c>
       <c r="AC383" t="s" s="1">
-        <v>5555</v>
+        <v>5535</v>
       </c>
       <c r="AD383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE383" t="s" s="1">
-        <v>5556</v>
+        <v>5536</v>
       </c>
       <c r="AF383" t="s" s="1">
-        <v>5557</v>
+        <v>5537</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="s" s="1">
-        <v>5558</v>
+        <v>5538</v>
       </c>
       <c r="B384" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C384" t="s" s="1">
+        <v>5539</v>
+      </c>
+      <c r="D384" t="s" s="1">
+        <v>5540</v>
+      </c>
+      <c r="E384" t="s" s="1">
+        <v>5541</v>
+      </c>
+      <c r="F384" t="s" s="1">
+        <v>5542</v>
+      </c>
+      <c r="G384" t="s" s="1">
+        <v>5543</v>
+      </c>
+      <c r="H384" t="s" s="1">
+        <v>5544</v>
+      </c>
+      <c r="I384" t="s" s="1">
+        <v>5545</v>
+      </c>
+      <c r="J384" t="s" s="1">
+        <v>5546</v>
+      </c>
+      <c r="K384" t="s" s="1">
+        <v>5547</v>
+      </c>
+      <c r="L384" t="s" s="1">
+        <v>5548</v>
+      </c>
+      <c r="M384" t="s" s="1">
+        <v>5549</v>
+      </c>
+      <c r="N384" t="s" s="1">
+        <v>5550</v>
+      </c>
+      <c r="O384" t="s" s="1">
+        <v>5551</v>
+      </c>
+      <c r="P384" t="s" s="1">
+        <v>5552</v>
+      </c>
+      <c r="Q384" t="s" s="1">
+        <v>5553</v>
+      </c>
+      <c r="R384" t="s" s="1">
+        <v>5554</v>
+      </c>
+      <c r="S384" t="s" s="1">
+        <v>5555</v>
+      </c>
+      <c r="T384" t="s" s="1">
+        <v>5556</v>
+      </c>
+      <c r="U384" t="s" s="1">
+        <v>5556</v>
+      </c>
+      <c r="V384" t="s" s="1">
+        <v>5557</v>
+      </c>
+      <c r="W384" t="s" s="1">
+        <v>5558</v>
+      </c>
+      <c r="X384" t="s" s="1">
         <v>5559</v>
       </c>
-      <c r="D384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E384" t="s" s="1">
-        <v>2295</v>
-      </c>
-      <c r="F384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G384" t="s" s="1">
+      <c r="Y384" t="s" s="1">
         <v>5560</v>
       </c>
-      <c r="H384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I384" t="s" s="1">
+      <c r="Z384" t="s" s="1">
         <v>5561</v>
       </c>
-      <c r="J384" t="s" s="1">
+      <c r="AA384" t="s" s="1">
         <v>5562</v>
       </c>
-      <c r="K384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M384" t="s" s="1">
+      <c r="AB384" t="s" s="1">
         <v>5563</v>
       </c>
-      <c r="N384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q384" t="s" s="1">
+      <c r="AC384" t="s" s="1">
         <v>5564</v>
       </c>
-      <c r="R384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S384" t="s" s="1">
+      <c r="AD384" t="s" s="1">
         <v>5565</v>
       </c>
-      <c r="T384" t="s" s="1">
+      <c r="AE384" t="s" s="1">
         <v>5566</v>
       </c>
-      <c r="U384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V384" t="s" s="1">
+      <c r="AF384" t="s" s="1">
         <v>5567</v>
-      </c>
-      <c r="W384" t="s" s="1">
-        <v>5568</v>
-      </c>
-      <c r="X384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC384" t="s" s="1">
-        <v>5569</v>
-      </c>
-      <c r="AD384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE384" t="s" s="1">
-        <v>5570</v>
-      </c>
-      <c r="AF384" t="s" s="1">
-        <v>5571</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s" s="1">
-        <v>5572</v>
+        <v>5568</v>
       </c>
       <c r="B385" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C385" t="s" s="1">
+        <v>5569</v>
+      </c>
+      <c r="D385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E385" t="s" s="1">
+        <v>5570</v>
+      </c>
+      <c r="F385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G385" t="s" s="1">
+        <v>5571</v>
+      </c>
+      <c r="H385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I385" t="s" s="1">
+        <v>3923</v>
+      </c>
+      <c r="J385" t="s" s="1">
+        <v>5572</v>
+      </c>
+      <c r="K385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M385" t="s" s="1">
+        <v>3921</v>
+      </c>
+      <c r="N385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S385" t="s" s="1">
         <v>5573</v>
       </c>
-      <c r="D385" t="s" s="1">
+      <c r="T385" t="s" s="1">
         <v>5574</v>
       </c>
-      <c r="E385" t="s" s="1">
+      <c r="U385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V385" t="s" s="1">
         <v>5575</v>
       </c>
-      <c r="F385" t="s" s="1">
+      <c r="W385" t="s" s="1">
         <v>5576</v>
       </c>
-      <c r="G385" t="s" s="1">
+      <c r="X385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC385" t="s" s="1">
         <v>5577</v>
       </c>
-      <c r="H385" t="s" s="1">
+      <c r="AD385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE385" t="s" s="1">
         <v>5578</v>
       </c>
-      <c r="I385" t="s" s="1">
+      <c r="AF385" t="s" s="1">
         <v>5579</v>
-      </c>
-      <c r="J385" t="s" s="1">
-        <v>5580</v>
-      </c>
-      <c r="K385" t="s" s="1">
-        <v>5581</v>
-      </c>
-      <c r="L385" t="s" s="1">
-        <v>5582</v>
-      </c>
-      <c r="M385" t="s" s="1">
-        <v>5579</v>
-      </c>
-      <c r="N385" t="s" s="1">
-        <v>5583</v>
-      </c>
-      <c r="O385" t="s" s="1">
-        <v>5584</v>
-      </c>
-      <c r="P385" t="s" s="1">
-        <v>5576</v>
-      </c>
-      <c r="Q385" t="s" s="1">
-        <v>5585</v>
-      </c>
-      <c r="R385" t="s" s="1">
-        <v>5576</v>
-      </c>
-      <c r="S385" t="s" s="1">
-        <v>5586</v>
-      </c>
-      <c r="T385" t="s" s="1">
-        <v>5587</v>
-      </c>
-      <c r="U385" t="s" s="1">
-        <v>5587</v>
-      </c>
-      <c r="V385" t="s" s="1">
-        <v>5588</v>
-      </c>
-      <c r="W385" t="s" s="1">
-        <v>5589</v>
-      </c>
-      <c r="X385" t="s" s="1">
-        <v>5590</v>
-      </c>
-      <c r="Y385" t="s" s="1">
-        <v>5591</v>
-      </c>
-      <c r="Z385" t="s" s="1">
-        <v>5592</v>
-      </c>
-      <c r="AA385" t="s" s="1">
-        <v>5593</v>
-      </c>
-      <c r="AB385" t="s" s="1">
-        <v>5594</v>
-      </c>
-      <c r="AC385" t="s" s="1">
-        <v>5595</v>
-      </c>
-      <c r="AD385" t="s" s="1">
-        <v>5596</v>
-      </c>
-      <c r="AE385" t="s" s="1">
-        <v>5597</v>
-      </c>
-      <c r="AF385" t="s" s="1">
-        <v>5598</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s" s="1">
-        <v>5599</v>
+        <v>5580</v>
       </c>
       <c r="B386" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C386" t="s" s="1">
-        <v>5600</v>
+        <v>5581</v>
       </c>
       <c r="D386" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E386" t="s" s="1">
-        <v>5601</v>
-      </c>
-      <c r="F386" t="s" s="1">
-        <v>5602</v>
+        <v>2295</v>
+      </c>
+      <c r="F386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="G386" t="s" s="1">
-        <v>5603</v>
-      </c>
-      <c r="H386" t="s" s="1">
-        <v>5604</v>
+        <v>5582</v>
+      </c>
+      <c r="H386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="I386" t="s" s="1">
-        <v>5605</v>
+        <v>5583</v>
       </c>
       <c r="J386" t="s" s="1">
-        <v>5606</v>
+        <v>5584</v>
       </c>
       <c r="K386" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="L386" t="s" s="1">
-        <v>5607</v>
+      <c r="L386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="M386" t="s" s="1">
-        <v>5608</v>
-      </c>
-      <c r="N386" t="s" s="1">
-        <v>5609</v>
-      </c>
-      <c r="O386" t="s" s="1">
-        <v>5610</v>
-      </c>
-      <c r="P386" t="s" s="1">
-        <v>5602</v>
+        <v>5585</v>
+      </c>
+      <c r="N386" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O386" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="Q386" t="s" s="1">
-        <v>5611</v>
-      </c>
-      <c r="R386" t="s" s="1">
-        <v>5612</v>
+        <v>5586</v>
+      </c>
+      <c r="R386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="S386" t="s" s="1">
-        <v>5613</v>
+        <v>5587</v>
       </c>
       <c r="T386" t="s" s="1">
-        <v>5614</v>
-      </c>
-      <c r="U386" t="s" s="1">
-        <v>5615</v>
+        <v>5588</v>
+      </c>
+      <c r="U386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="V386" t="s" s="1">
-        <v>5616</v>
+        <v>5589</v>
       </c>
       <c r="W386" t="s" s="1">
-        <v>5617</v>
+        <v>5590</v>
       </c>
       <c r="X386" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="Y386" t="s" s="1">
-        <v>5618</v>
+      <c r="Y386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="Z386" t="s" s="2">
         <v>63</v>
@@ -78011,248 +78077,248 @@
       <c r="AA386" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="AB386" t="s" s="1">
-        <v>5619</v>
+      <c r="AB386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AC386" t="s" s="1">
-        <v>5620</v>
-      </c>
-      <c r="AD386" t="s" s="1">
-        <v>5621</v>
+        <v>5591</v>
+      </c>
+      <c r="AD386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AE386" t="s" s="1">
-        <v>5622</v>
+        <v>5592</v>
       </c>
       <c r="AF386" t="s" s="1">
-        <v>5623</v>
+        <v>5593</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s" s="1">
-        <v>5624</v>
+        <v>5594</v>
       </c>
       <c r="B387" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C387" t="s" s="1">
-        <v>5625</v>
-      </c>
-      <c r="D387" t="s" s="2">
-        <v>63</v>
+        <v>5595</v>
+      </c>
+      <c r="D387" t="s" s="1">
+        <v>5596</v>
       </c>
       <c r="E387" t="s" s="1">
-        <v>5626</v>
-      </c>
-      <c r="F387" t="s" s="2">
-        <v>63</v>
+        <v>5597</v>
+      </c>
+      <c r="F387" t="s" s="1">
+        <v>5598</v>
       </c>
       <c r="G387" t="s" s="1">
-        <v>5627</v>
-      </c>
-      <c r="H387" t="s" s="2">
-        <v>63</v>
+        <v>5599</v>
+      </c>
+      <c r="H387" t="s" s="1">
+        <v>5600</v>
       </c>
       <c r="I387" t="s" s="1">
-        <v>5628</v>
+        <v>5601</v>
       </c>
       <c r="J387" t="s" s="1">
-        <v>5629</v>
-      </c>
-      <c r="K387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="N387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S387" t="s" s="2">
-        <v>63</v>
+        <v>5602</v>
+      </c>
+      <c r="K387" t="s" s="1">
+        <v>5603</v>
+      </c>
+      <c r="L387" t="s" s="1">
+        <v>5604</v>
+      </c>
+      <c r="M387" t="s" s="1">
+        <v>5601</v>
+      </c>
+      <c r="N387" t="s" s="1">
+        <v>5605</v>
+      </c>
+      <c r="O387" t="s" s="1">
+        <v>5606</v>
+      </c>
+      <c r="P387" t="s" s="1">
+        <v>5598</v>
+      </c>
+      <c r="Q387" t="s" s="1">
+        <v>5607</v>
+      </c>
+      <c r="R387" t="s" s="1">
+        <v>5598</v>
+      </c>
+      <c r="S387" t="s" s="1">
+        <v>5608</v>
       </c>
       <c r="T387" t="s" s="1">
-        <v>5630</v>
-      </c>
-      <c r="U387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="W387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="X387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB387" t="s" s="2">
-        <v>63</v>
+        <v>5609</v>
+      </c>
+      <c r="U387" t="s" s="1">
+        <v>5609</v>
+      </c>
+      <c r="V387" t="s" s="1">
+        <v>5610</v>
+      </c>
+      <c r="W387" t="s" s="1">
+        <v>5611</v>
+      </c>
+      <c r="X387" t="s" s="1">
+        <v>5612</v>
+      </c>
+      <c r="Y387" t="s" s="1">
+        <v>5613</v>
+      </c>
+      <c r="Z387" t="s" s="1">
+        <v>5614</v>
+      </c>
+      <c r="AA387" t="s" s="1">
+        <v>5615</v>
+      </c>
+      <c r="AB387" t="s" s="1">
+        <v>5616</v>
       </c>
       <c r="AC387" t="s" s="1">
-        <v>5631</v>
-      </c>
-      <c r="AD387" t="s" s="2">
-        <v>63</v>
+        <v>5617</v>
+      </c>
+      <c r="AD387" t="s" s="1">
+        <v>5618</v>
       </c>
       <c r="AE387" t="s" s="1">
-        <v>5632</v>
-      </c>
-      <c r="AF387" t="s" s="2">
-        <v>63</v>
+        <v>5619</v>
+      </c>
+      <c r="AF387" t="s" s="1">
+        <v>5620</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="s" s="1">
-        <v>5633</v>
+        <v>5621</v>
       </c>
       <c r="B388" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C388" t="s" s="1">
+        <v>5622</v>
+      </c>
+      <c r="D388" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E388" t="s" s="1">
+        <v>5623</v>
+      </c>
+      <c r="F388" t="s" s="1">
+        <v>5624</v>
+      </c>
+      <c r="G388" t="s" s="1">
+        <v>5625</v>
+      </c>
+      <c r="H388" t="s" s="1">
+        <v>5626</v>
+      </c>
+      <c r="I388" t="s" s="1">
+        <v>5627</v>
+      </c>
+      <c r="J388" t="s" s="1">
+        <v>5628</v>
+      </c>
+      <c r="K388" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L388" t="s" s="1">
+        <v>5629</v>
+      </c>
+      <c r="M388" t="s" s="1">
+        <v>5630</v>
+      </c>
+      <c r="N388" t="s" s="1">
+        <v>5631</v>
+      </c>
+      <c r="O388" t="s" s="1">
+        <v>5632</v>
+      </c>
+      <c r="P388" t="s" s="1">
+        <v>5624</v>
+      </c>
+      <c r="Q388" t="s" s="1">
+        <v>5633</v>
+      </c>
+      <c r="R388" t="s" s="1">
         <v>5634</v>
       </c>
-      <c r="D388" t="s" s="1">
+      <c r="S388" t="s" s="1">
         <v>5635</v>
       </c>
-      <c r="E388" t="s" s="1">
+      <c r="T388" t="s" s="1">
         <v>5636</v>
       </c>
-      <c r="F388" t="s" s="1">
+      <c r="U388" t="s" s="1">
         <v>5637</v>
       </c>
-      <c r="G388" t="s" s="1">
+      <c r="V388" t="s" s="1">
         <v>5638</v>
       </c>
-      <c r="H388" t="s" s="1">
+      <c r="W388" t="s" s="1">
         <v>5639</v>
       </c>
-      <c r="I388" t="s" s="1">
+      <c r="X388" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y388" t="s" s="1">
         <v>5640</v>
       </c>
-      <c r="J388" t="s" s="1">
+      <c r="Z388" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA388" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB388" t="s" s="1">
         <v>5641</v>
       </c>
-      <c r="K388" t="s" s="1">
+      <c r="AC388" t="s" s="1">
         <v>5642</v>
       </c>
-      <c r="L388" t="s" s="1">
+      <c r="AD388" t="s" s="1">
         <v>5643</v>
       </c>
-      <c r="M388" t="s" s="1">
+      <c r="AE388" t="s" s="1">
         <v>5644</v>
       </c>
-      <c r="N388" t="s" s="1">
+      <c r="AF388" t="s" s="1">
         <v>5645</v>
-      </c>
-      <c r="O388" t="s" s="1">
-        <v>5646</v>
-      </c>
-      <c r="P388" t="s" s="1">
-        <v>5647</v>
-      </c>
-      <c r="Q388" t="s" s="1">
-        <v>5648</v>
-      </c>
-      <c r="R388" t="s" s="1">
-        <v>5649</v>
-      </c>
-      <c r="S388" t="s" s="1">
-        <v>5650</v>
-      </c>
-      <c r="T388" t="s" s="1">
-        <v>5651</v>
-      </c>
-      <c r="U388" t="s" s="1">
-        <v>5651</v>
-      </c>
-      <c r="V388" t="s" s="1">
-        <v>5652</v>
-      </c>
-      <c r="W388" t="s" s="1">
-        <v>5653</v>
-      </c>
-      <c r="X388" t="s" s="1">
-        <v>5654</v>
-      </c>
-      <c r="Y388" t="s" s="1">
-        <v>5655</v>
-      </c>
-      <c r="Z388" t="s" s="1">
-        <v>5656</v>
-      </c>
-      <c r="AA388" t="s" s="1">
-        <v>5657</v>
-      </c>
-      <c r="AB388" t="s" s="1">
-        <v>5658</v>
-      </c>
-      <c r="AC388" t="s" s="1">
-        <v>5659</v>
-      </c>
-      <c r="AD388" t="s" s="1">
-        <v>5660</v>
-      </c>
-      <c r="AE388" t="s" s="1">
-        <v>5661</v>
-      </c>
-      <c r="AF388" t="s" s="1">
-        <v>5662</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="s" s="1">
-        <v>5663</v>
+        <v>5646</v>
       </c>
       <c r="B389" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C389" t="s" s="1">
-        <v>5664</v>
+        <v>5647</v>
       </c>
       <c r="D389" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E389" t="s" s="1">
-        <v>5665</v>
+        <v>5648</v>
       </c>
       <c r="F389" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G389" t="s" s="1">
-        <v>5666</v>
+        <v>5649</v>
       </c>
       <c r="H389" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I389" t="s" s="1">
-        <v>5667</v>
+        <v>5650</v>
       </c>
       <c r="J389" t="s" s="1">
-        <v>5668</v>
+        <v>5651</v>
       </c>
       <c r="K389" t="s" s="2">
         <v>63</v>
@@ -78260,8 +78326,8 @@
       <c r="L389" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="M389" t="s" s="1">
-        <v>5669</v>
+      <c r="M389" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="N389" t="s" s="2">
         <v>63</v>
@@ -78272,26 +78338,26 @@
       <c r="P389" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="Q389" t="s" s="1">
-        <v>5670</v>
+      <c r="Q389" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="R389" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="S389" t="s" s="1">
-        <v>5671</v>
+      <c r="S389" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="T389" t="s" s="1">
-        <v>5672</v>
+        <v>5652</v>
       </c>
       <c r="U389" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="V389" t="s" s="1">
-        <v>5673</v>
-      </c>
-      <c r="W389" t="s" s="1">
-        <v>5674</v>
+      <c r="V389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="W389" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="X389" t="s" s="2">
         <v>63</v>
@@ -78309,510 +78375,706 @@
         <v>63</v>
       </c>
       <c r="AC389" t="s" s="1">
-        <v>5675</v>
+        <v>5653</v>
       </c>
       <c r="AD389" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE389" t="s" s="1">
-        <v>5676</v>
-      </c>
-      <c r="AF389" t="s" s="1">
-        <v>5677</v>
+        <v>5654</v>
+      </c>
+      <c r="AF389" t="s" s="2">
+        <v>63</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="s" s="1">
-        <v>5678</v>
+        <v>5655</v>
       </c>
       <c r="B390" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C390" t="s" s="1">
+        <v>5656</v>
+      </c>
+      <c r="D390" t="s" s="1">
+        <v>5657</v>
+      </c>
+      <c r="E390" t="s" s="1">
+        <v>5658</v>
+      </c>
+      <c r="F390" t="s" s="1">
+        <v>5659</v>
+      </c>
+      <c r="G390" t="s" s="1">
+        <v>5660</v>
+      </c>
+      <c r="H390" t="s" s="1">
+        <v>5661</v>
+      </c>
+      <c r="I390" t="s" s="1">
+        <v>5662</v>
+      </c>
+      <c r="J390" t="s" s="1">
+        <v>5663</v>
+      </c>
+      <c r="K390" t="s" s="1">
+        <v>5664</v>
+      </c>
+      <c r="L390" t="s" s="1">
+        <v>5665</v>
+      </c>
+      <c r="M390" t="s" s="1">
+        <v>5666</v>
+      </c>
+      <c r="N390" t="s" s="1">
+        <v>5667</v>
+      </c>
+      <c r="O390" t="s" s="1">
+        <v>5668</v>
+      </c>
+      <c r="P390" t="s" s="1">
+        <v>5669</v>
+      </c>
+      <c r="Q390" t="s" s="1">
+        <v>5670</v>
+      </c>
+      <c r="R390" t="s" s="1">
+        <v>5671</v>
+      </c>
+      <c r="S390" t="s" s="1">
+        <v>5672</v>
+      </c>
+      <c r="T390" t="s" s="1">
+        <v>5673</v>
+      </c>
+      <c r="U390" t="s" s="1">
+        <v>5673</v>
+      </c>
+      <c r="V390" t="s" s="1">
+        <v>5674</v>
+      </c>
+      <c r="W390" t="s" s="1">
+        <v>5675</v>
+      </c>
+      <c r="X390" t="s" s="1">
+        <v>5676</v>
+      </c>
+      <c r="Y390" t="s" s="1">
+        <v>5677</v>
+      </c>
+      <c r="Z390" t="s" s="1">
+        <v>5678</v>
+      </c>
+      <c r="AA390" t="s" s="1">
         <v>5679</v>
       </c>
-      <c r="D390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E390" t="s" s="1">
+      <c r="AB390" t="s" s="1">
         <v>5680</v>
       </c>
-      <c r="F390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G390" t="s" s="1">
+      <c r="AC390" t="s" s="1">
         <v>5681</v>
       </c>
-      <c r="H390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I390" t="s" s="1">
+      <c r="AD390" t="s" s="1">
         <v>5682</v>
       </c>
-      <c r="J390" t="s" s="1">
+      <c r="AE390" t="s" s="1">
         <v>5683</v>
       </c>
-      <c r="K390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M390" t="s" s="1">
+      <c r="AF390" t="s" s="1">
         <v>5684</v>
-      </c>
-      <c r="N390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S390" t="s" s="1">
-        <v>5685</v>
-      </c>
-      <c r="T390" t="s" s="1">
-        <v>5682</v>
-      </c>
-      <c r="U390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V390" t="s" s="1">
-        <v>5686</v>
-      </c>
-      <c r="W390" t="s" s="1">
-        <v>5687</v>
-      </c>
-      <c r="X390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC390" t="s" s="1">
-        <v>5688</v>
-      </c>
-      <c r="AD390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE390" t="s" s="1">
-        <v>5689</v>
-      </c>
-      <c r="AF390" t="s" s="1">
-        <v>5690</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="s" s="1">
-        <v>5691</v>
+        <v>5685</v>
       </c>
       <c r="B391" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C391" t="s" s="1">
+        <v>5686</v>
+      </c>
+      <c r="D391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E391" t="s" s="1">
+        <v>5687</v>
+      </c>
+      <c r="F391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G391" t="s" s="1">
+        <v>5688</v>
+      </c>
+      <c r="H391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I391" t="s" s="1">
+        <v>5689</v>
+      </c>
+      <c r="J391" t="s" s="1">
+        <v>5690</v>
+      </c>
+      <c r="K391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M391" t="s" s="1">
+        <v>5691</v>
+      </c>
+      <c r="N391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q391" t="s" s="1">
         <v>5692</v>
       </c>
-      <c r="D391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E391" t="s" s="1">
+      <c r="R391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S391" t="s" s="1">
         <v>5693</v>
       </c>
-      <c r="F391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G391" t="s" s="1">
+      <c r="T391" t="s" s="1">
         <v>5694</v>
       </c>
-      <c r="H391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I391" t="s" s="1">
+      <c r="U391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V391" t="s" s="1">
         <v>5695</v>
       </c>
-      <c r="J391" t="s" s="1">
+      <c r="W391" t="s" s="1">
         <v>5696</v>
       </c>
-      <c r="K391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M391" t="s" s="1">
+      <c r="X391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC391" t="s" s="1">
         <v>5697</v>
       </c>
-      <c r="N391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q391" t="s" s="1">
+      <c r="AD391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE391" t="s" s="1">
         <v>5698</v>
       </c>
-      <c r="R391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S391" t="s" s="1">
+      <c r="AF391" t="s" s="1">
         <v>5699</v>
-      </c>
-      <c r="T391" t="s" s="1">
-        <v>5700</v>
-      </c>
-      <c r="U391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V391" t="s" s="1">
-        <v>5701</v>
-      </c>
-      <c r="W391" t="s" s="1">
-        <v>5702</v>
-      </c>
-      <c r="X391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC391" t="s" s="1">
-        <v>5703</v>
-      </c>
-      <c r="AD391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE391" t="s" s="1">
-        <v>5704</v>
-      </c>
-      <c r="AF391" t="s" s="1">
-        <v>5705</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="s" s="1">
-        <v>5706</v>
+        <v>5700</v>
       </c>
       <c r="B392" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C392" t="s" s="1">
+        <v>5701</v>
+      </c>
+      <c r="D392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E392" t="s" s="1">
+        <v>5702</v>
+      </c>
+      <c r="F392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G392" t="s" s="1">
+        <v>5703</v>
+      </c>
+      <c r="H392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I392" t="s" s="1">
+        <v>5704</v>
+      </c>
+      <c r="J392" t="s" s="1">
+        <v>5705</v>
+      </c>
+      <c r="K392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M392" t="s" s="1">
+        <v>5706</v>
+      </c>
+      <c r="N392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S392" t="s" s="1">
         <v>5707</v>
       </c>
-      <c r="D392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E392" t="s" s="1">
+      <c r="T392" t="s" s="1">
+        <v>5704</v>
+      </c>
+      <c r="U392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V392" t="s" s="1">
         <v>5708</v>
       </c>
-      <c r="F392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G392" t="s" s="1">
+      <c r="W392" t="s" s="1">
         <v>5709</v>
       </c>
-      <c r="H392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I392" t="s" s="1">
+      <c r="X392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC392" t="s" s="1">
         <v>5710</v>
       </c>
-      <c r="J392" t="s" s="1">
+      <c r="AD392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE392" t="s" s="1">
         <v>5711</v>
       </c>
-      <c r="K392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M392" t="s" s="1">
+      <c r="AF392" t="s" s="1">
         <v>5712</v>
-      </c>
-      <c r="N392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S392" t="s" s="1">
-        <v>5713</v>
-      </c>
-      <c r="T392" t="s" s="1">
-        <v>5714</v>
-      </c>
-      <c r="U392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V392" t="s" s="1">
-        <v>5710</v>
-      </c>
-      <c r="W392" t="s" s="1">
-        <v>5715</v>
-      </c>
-      <c r="X392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC392" t="s" s="1">
-        <v>5716</v>
-      </c>
-      <c r="AD392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE392" t="s" s="1">
-        <v>5717</v>
-      </c>
-      <c r="AF392" t="s" s="1">
-        <v>5718</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="s" s="1">
-        <v>5719</v>
+        <v>5713</v>
       </c>
       <c r="B393" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C393" t="s" s="1">
+        <v>5714</v>
+      </c>
+      <c r="D393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E393" t="s" s="1">
+        <v>5715</v>
+      </c>
+      <c r="F393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G393" t="s" s="1">
+        <v>5716</v>
+      </c>
+      <c r="H393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I393" t="s" s="1">
+        <v>5717</v>
+      </c>
+      <c r="J393" t="s" s="1">
+        <v>5718</v>
+      </c>
+      <c r="K393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M393" t="s" s="1">
+        <v>5719</v>
+      </c>
+      <c r="N393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q393" t="s" s="1">
         <v>5720</v>
       </c>
-      <c r="D393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E393" t="s" s="1">
+      <c r="R393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S393" t="s" s="1">
         <v>5721</v>
       </c>
-      <c r="F393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G393" t="s" s="1">
+      <c r="T393" t="s" s="1">
         <v>5722</v>
       </c>
-      <c r="H393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I393" t="s" s="1">
+      <c r="U393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V393" t="s" s="1">
         <v>5723</v>
       </c>
-      <c r="J393" t="s" s="1">
+      <c r="W393" t="s" s="1">
         <v>5724</v>
       </c>
-      <c r="K393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M393" t="s" s="1">
+      <c r="X393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC393" t="s" s="1">
         <v>5725</v>
       </c>
-      <c r="N393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S393" t="s" s="1">
+      <c r="AD393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE393" t="s" s="1">
         <v>5726</v>
       </c>
-      <c r="T393" t="s" s="1">
+      <c r="AF393" t="s" s="1">
         <v>5727</v>
-      </c>
-      <c r="U393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V393" t="s" s="1">
-        <v>5728</v>
-      </c>
-      <c r="W393" t="s" s="1">
-        <v>5729</v>
-      </c>
-      <c r="X393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC393" t="s" s="1">
-        <v>5730</v>
-      </c>
-      <c r="AD393" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE393" t="s" s="1">
-        <v>5731</v>
-      </c>
-      <c r="AF393" t="s" s="1">
-        <v>5732</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="s" s="1">
-        <v>5733</v>
+        <v>5728</v>
       </c>
       <c r="B394" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C394" t="s" s="1">
+        <v>5729</v>
+      </c>
+      <c r="D394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E394" t="s" s="1">
+        <v>5730</v>
+      </c>
+      <c r="F394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G394" t="s" s="1">
+        <v>5731</v>
+      </c>
+      <c r="H394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I394" t="s" s="1">
+        <v>5732</v>
+      </c>
+      <c r="J394" t="s" s="1">
+        <v>5733</v>
+      </c>
+      <c r="K394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M394" t="s" s="1">
         <v>5734</v>
       </c>
-      <c r="D394" t="s" s="1">
+      <c r="N394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S394" t="s" s="1">
         <v>5735</v>
       </c>
-      <c r="E394" t="s" s="1">
+      <c r="T394" t="s" s="1">
         <v>5736</v>
       </c>
-      <c r="F394" t="s" s="1">
+      <c r="U394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V394" t="s" s="1">
+        <v>5732</v>
+      </c>
+      <c r="W394" t="s" s="1">
         <v>5737</v>
       </c>
-      <c r="G394" t="s" s="1">
+      <c r="X394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC394" t="s" s="1">
         <v>5738</v>
       </c>
-      <c r="H394" t="s" s="1">
+      <c r="AD394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE394" t="s" s="1">
         <v>5739</v>
       </c>
-      <c r="I394" t="s" s="1">
+      <c r="AF394" t="s" s="1">
         <v>5740</v>
       </c>
-      <c r="J394" t="s" s="1">
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="1">
         <v>5741</v>
       </c>
-      <c r="K394" t="s" s="1">
+      <c r="B395" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="C395" t="s" s="1">
         <v>5742</v>
       </c>
-      <c r="L394" t="s" s="1">
+      <c r="D395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E395" t="s" s="1">
         <v>5743</v>
       </c>
-      <c r="M394" t="s" s="1">
+      <c r="F395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G395" t="s" s="1">
         <v>5744</v>
       </c>
-      <c r="N394" t="s" s="1">
+      <c r="H395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I395" t="s" s="1">
         <v>5745</v>
       </c>
-      <c r="O394" t="s" s="1">
+      <c r="J395" t="s" s="1">
         <v>5746</v>
       </c>
-      <c r="P394" t="s" s="1">
+      <c r="K395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M395" t="s" s="1">
         <v>5747</v>
       </c>
-      <c r="Q394" t="s" s="1">
+      <c r="N395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S395" t="s" s="1">
         <v>5748</v>
       </c>
-      <c r="R394" t="s" s="1">
+      <c r="T395" t="s" s="1">
         <v>5749</v>
       </c>
-      <c r="S394" t="s" s="1">
+      <c r="U395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V395" t="s" s="1">
         <v>5750</v>
       </c>
-      <c r="T394" t="s" s="1">
+      <c r="W395" t="s" s="1">
         <v>5751</v>
       </c>
-      <c r="U394" t="s" s="1">
+      <c r="X395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC395" t="s" s="1">
         <v>5752</v>
       </c>
-      <c r="V394" t="s" s="1">
+      <c r="AD395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE395" t="s" s="1">
         <v>5753</v>
       </c>
-      <c r="W394" t="s" s="1">
+      <c r="AF395" t="s" s="1">
         <v>5754</v>
       </c>
-      <c r="X394" t="s" s="1">
+    </row>
+    <row r="396">
+      <c r="A396" t="s" s="1">
         <v>5755</v>
       </c>
-      <c r="Y394" t="s" s="1">
+      <c r="B396" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="C396" t="s" s="1">
         <v>5756</v>
       </c>
-      <c r="Z394" t="s" s="1">
+      <c r="D396" t="s" s="1">
         <v>5757</v>
       </c>
-      <c r="AA394" t="s" s="1">
+      <c r="E396" t="s" s="1">
         <v>5758</v>
       </c>
-      <c r="AB394" t="s" s="1">
+      <c r="F396" t="s" s="1">
         <v>5759</v>
       </c>
-      <c r="AC394" t="s" s="1">
+      <c r="G396" t="s" s="1">
         <v>5760</v>
       </c>
-      <c r="AD394" t="s" s="1">
+      <c r="H396" t="s" s="1">
         <v>5761</v>
       </c>
-      <c r="AE394" t="s" s="1">
+      <c r="I396" t="s" s="1">
         <v>5762</v>
       </c>
-      <c r="AF394" t="s" s="1">
+      <c r="J396" t="s" s="1">
         <v>5763</v>
+      </c>
+      <c r="K396" t="s" s="1">
+        <v>5764</v>
+      </c>
+      <c r="L396" t="s" s="1">
+        <v>5765</v>
+      </c>
+      <c r="M396" t="s" s="1">
+        <v>5766</v>
+      </c>
+      <c r="N396" t="s" s="1">
+        <v>5767</v>
+      </c>
+      <c r="O396" t="s" s="1">
+        <v>5768</v>
+      </c>
+      <c r="P396" t="s" s="1">
+        <v>5769</v>
+      </c>
+      <c r="Q396" t="s" s="1">
+        <v>5770</v>
+      </c>
+      <c r="R396" t="s" s="1">
+        <v>5771</v>
+      </c>
+      <c r="S396" t="s" s="1">
+        <v>5772</v>
+      </c>
+      <c r="T396" t="s" s="1">
+        <v>5773</v>
+      </c>
+      <c r="U396" t="s" s="1">
+        <v>5774</v>
+      </c>
+      <c r="V396" t="s" s="1">
+        <v>5775</v>
+      </c>
+      <c r="W396" t="s" s="1">
+        <v>5776</v>
+      </c>
+      <c r="X396" t="s" s="1">
+        <v>5777</v>
+      </c>
+      <c r="Y396" t="s" s="1">
+        <v>5778</v>
+      </c>
+      <c r="Z396" t="s" s="1">
+        <v>5779</v>
+      </c>
+      <c r="AA396" t="s" s="1">
+        <v>5780</v>
+      </c>
+      <c r="AB396" t="s" s="1">
+        <v>5781</v>
+      </c>
+      <c r="AC396" t="s" s="1">
+        <v>5782</v>
+      </c>
+      <c r="AD396" t="s" s="1">
+        <v>5783</v>
+      </c>
+      <c r="AE396" t="s" s="1">
+        <v>5784</v>
+      </c>
+      <c r="AF396" t="s" s="1">
+        <v>5785</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG394"/>
+  <autoFilter ref="A1:AG396"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>

--- a/app/translations.xlsx
+++ b/app/translations.xlsx
@@ -17471,7 +17471,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13728" uniqueCount="6260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13728" uniqueCount="6261">
   <si>
     <t>Key</t>
   </si>
@@ -23742,6 +23742,9 @@
     <t>Видалити нагадування?</t>
   </si>
   <si>
+    <t>删除提醒？</t>
+  </si>
+  <si>
     <t>delete_reminder_question</t>
   </si>
   <si>
@@ -23773,9 +23776,6 @@
   </si>
   <si>
     <t>Удалить напоминание?</t>
-  </si>
-  <si>
-    <t>删除提醒？</t>
   </si>
   <si>
     <t>刪除提醒?</t>
@@ -36460,6 +36460,9 @@
   </si>
   <si>
     <t>Застосовувати також у режимі перегляду нотатки</t>
+  </si>
+  <si>
+    <t>同样应用于笔记视图</t>
   </si>
 </sst>
 </file>
@@ -55946,8 +55949,8 @@
       <c r="AE134" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="AF134" t="s" s="2">
-        <v>66</v>
+      <c r="AF134" t="s" s="1">
+        <v>2051</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>66</v>
@@ -55955,28 +55958,28 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="1">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="B135" t="s" s="1">
         <v>34</v>
       </c>
       <c r="C135" t="s" s="1">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="D135" t="s" s="1">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="E135" t="s" s="2">
         <v>66</v>
       </c>
       <c r="F135" t="s" s="1">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>66</v>
       </c>
       <c r="H135" t="s" s="1">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>66</v>
@@ -55985,7 +55988,7 @@
         <v>66</v>
       </c>
       <c r="K135" t="s" s="1">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="L135" t="s" s="2">
         <v>66</v>
@@ -55994,7 +55997,7 @@
         <v>66</v>
       </c>
       <c r="N135" t="s" s="1">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="O135" t="s" s="2">
         <v>66</v>
@@ -56012,19 +56015,19 @@
         <v>66</v>
       </c>
       <c r="T135" t="s" s="1">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="U135" t="s" s="1">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="V135" t="s" s="2">
         <v>66</v>
       </c>
       <c r="W135" t="s" s="1">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="X135" t="s" s="1">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="Y135" t="s" s="2">
         <v>66</v>
@@ -56047,8 +56050,8 @@
       <c r="AE135" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="AF135" t="s" s="1">
-        <v>2062</v>
+      <c r="AF135" t="s" s="2">
+        <v>66</v>
       </c>
       <c r="AG135" t="s" s="1">
         <v>2063</v>
@@ -84428,8 +84431,8 @@
       <c r="AE416" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="AF416" t="s" s="2">
-        <v>66</v>
+      <c r="AF416" t="s" s="1">
+        <v>6260</v>
       </c>
       <c r="AG416" t="s" s="2">
         <v>66</v>
